--- a/data/trans_orig/imc_inf-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/imc_inf-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores, declarado por los/as progenitores/as</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, declarado por los/as progenitores/as (tasa de respuesta: 87,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,26; 19,3</t>
+          <t>18,26; 19,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,67; 20,45</t>
+          <t>18,68; 20,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,47 +731,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,3; 19,74</t>
+          <t>18,45; 19,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,86; 19,96</t>
+          <t>18,95; 19,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,4; 21,0</t>
+          <t>19,41; 20,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,79; 20,27</t>
+          <t>18,77; 20,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,96; 22,22</t>
+          <t>18,94; 22,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,77; 19,53</t>
+          <t>18,78; 19,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,26; 20,44</t>
+          <t>19,23; 20,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,88; 19,86</t>
+          <t>18,91; 19,9</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,96; 21,1</t>
+          <t>19,02; 21,14</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,77; 19,62</t>
+          <t>18,77; 19,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,38; 19,44</t>
+          <t>18,41; 19,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,95; 18,81</t>
+          <t>17,96; 18,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,98; 19,18</t>
+          <t>18,01; 19,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,19; 20,5</t>
+          <t>19,24; 20,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,37; 21,1</t>
+          <t>19,42; 21,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,6; 19,88</t>
+          <t>18,55; 19,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,0; 20,06</t>
+          <t>19,02; 20,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,13; 19,93</t>
+          <t>19,14; 19,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,09; 20,08</t>
+          <t>19,07; 20,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,44; 19,24</t>
+          <t>18,43; 19,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,67; 19,51</t>
+          <t>18,68; 19,5</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,89; 20,44</t>
+          <t>18,89; 20,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,79; 20,28</t>
+          <t>18,79; 20,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,91; 19,15</t>
+          <t>17,9; 19,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,41; 21,22</t>
+          <t>18,45; 21,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,66; 22,03</t>
+          <t>19,5; 21,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,82; 20,72</t>
+          <t>18,96; 20,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,68; 18,85</t>
+          <t>17,66; 18,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,47; 20,12</t>
+          <t>18,47; 20,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,43; 20,85</t>
+          <t>19,44; 20,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,09; 20,23</t>
+          <t>19,08; 20,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,93; 18,77</t>
+          <t>17,91; 18,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,71; 20,44</t>
+          <t>18,73; 20,44</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,18; 19,27</t>
+          <t>18,19; 19,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,87; 20,01</t>
+          <t>18,85; 20,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,72; 20,21</t>
+          <t>18,75; 20,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,13; 19,8</t>
+          <t>18,13; 19,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,92; 20,57</t>
+          <t>18,97; 20,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,17; 21,57</t>
+          <t>19,11; 21,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,91; 20,51</t>
+          <t>18,9; 20,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,06; 19,05</t>
+          <t>18,07; 19,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,67; 19,59</t>
+          <t>18,69; 19,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,15; 20,53</t>
+          <t>19,17; 20,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,96; 19,99</t>
+          <t>18,96; 20,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,23; 19,19</t>
+          <t>18,25; 19,23</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,75; 19,3</t>
+          <t>18,76; 19,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,99; 19,62</t>
+          <t>18,99; 19,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,55; 19,16</t>
+          <t>18,54; 19,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,53; 19,62</t>
+          <t>18,57; 19,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,45; 20,22</t>
+          <t>19,4; 20,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,56; 20,52</t>
+          <t>19,52; 20,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,8; 19,51</t>
+          <t>18,79; 19,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,95; 19,79</t>
+          <t>18,9; 19,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,18; 19,68</t>
+          <t>19,19; 19,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,37; 19,93</t>
+          <t>19,35; 19,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,73; 19,2</t>
+          <t>18,74; 19,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,84; 19,54</t>
+          <t>18,86; 19,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/imc_inf-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/imc_inf-Habitat-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,26; 19,4</t>
+          <t>18,29; 19,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,68; 20,47</t>
+          <t>18,67; 20,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,61; 19,9</t>
+          <t>18,62; 19,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,45; 19,88</t>
+          <t>18,35; 19,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,95; 19,98</t>
+          <t>18,92; 19,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,41; 20,9</t>
+          <t>19,37; 20,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,77; 20,22</t>
+          <t>18,7; 20,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,94; 22,5</t>
+          <t>19,03; 22,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,78; 19,54</t>
+          <t>18,8; 19,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,23; 20,35</t>
+          <t>19,16; 20,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,91; 19,9</t>
+          <t>18,87; 19,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,02; 21,14</t>
+          <t>18,91; 20,85</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,77; 19,61</t>
+          <t>18,77; 19,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,41; 19,44</t>
+          <t>18,4; 19,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,96; 18,86</t>
+          <t>17,99; 18,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,01; 19,19</t>
+          <t>18,0; 19,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,24; 20,69</t>
+          <t>19,22; 20,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,42; 21,13</t>
+          <t>19,38; 20,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,55; 19,79</t>
+          <t>18,65; 19,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,02; 20,06</t>
+          <t>18,99; 20,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,14; 19,97</t>
+          <t>19,1; 19,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,07; 20,05</t>
+          <t>19,1; 20,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,43; 19,25</t>
+          <t>18,42; 19,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,68; 19,5</t>
+          <t>18,71; 19,52</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,89; 20,38</t>
+          <t>18,87; 20,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,79; 20,37</t>
+          <t>18,77; 20,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,9; 19,25</t>
+          <t>17,87; 19,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,45; 21,13</t>
+          <t>18,43; 21,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,5; 21,82</t>
+          <t>19,58; 21,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,96; 20,89</t>
+          <t>18,95; 20,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,66; 18,7</t>
+          <t>17,66; 18,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,47; 20,08</t>
+          <t>18,52; 20,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,44; 20,89</t>
+          <t>19,51; 20,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,08; 20,24</t>
+          <t>19,09; 20,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,91; 18,79</t>
+          <t>17,93; 18,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,73; 20,44</t>
+          <t>18,72; 20,57</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,19; 19,29</t>
+          <t>18,16; 19,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,85; 20,08</t>
+          <t>18,86; 20,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,75; 20,16</t>
+          <t>18,74; 20,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,13; 19,75</t>
+          <t>18,12; 19,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,97; 20,62</t>
+          <t>18,93; 20,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,11; 21,55</t>
+          <t>19,11; 21,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,9; 20,55</t>
+          <t>18,86; 20,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,07; 19,16</t>
+          <t>18,05; 19,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,69; 19,71</t>
+          <t>18,7; 19,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,17; 20,55</t>
+          <t>19,19; 20,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,96; 20,0</t>
+          <t>18,95; 20,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,25; 19,23</t>
+          <t>18,25; 19,22</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,76; 19,34</t>
+          <t>18,72; 19,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,99; 19,63</t>
+          <t>18,97; 19,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,54; 19,17</t>
+          <t>18,53; 19,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,57; 19,73</t>
+          <t>18,56; 19,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,4; 20,19</t>
+          <t>19,46; 20,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,52; 20,45</t>
+          <t>19,55; 20,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,79; 19,51</t>
+          <t>18,75; 19,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,9; 19,75</t>
+          <t>18,94; 19,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,19; 19,68</t>
+          <t>19,18; 19,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,35; 19,92</t>
+          <t>19,35; 19,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,74; 19,2</t>
+          <t>18,73; 19,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,86; 19,51</t>
+          <t>18,87; 19,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/imc_inf-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/imc_inf-Habitat-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19,46</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20,05</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19,46</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20,32</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>18,78</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>19,44</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>19,22</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19,02</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19,46</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,05</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,46</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,1</t>
+          <t>19,04</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,62</t>
+          <t>19,7</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,29; 19,32</t>
+          <t>18,86; 19,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,67; 20,37</t>
+          <t>19,4; 21,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,62; 19,99</t>
+          <t>18,79; 20,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,35; 19,73</t>
+          <t>19,15; 22,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,92; 19,95</t>
+          <t>18,26; 19,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,37; 20,83</t>
+          <t>18,67; 20,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,7; 20,29</t>
+          <t>18,61; 19,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,03; 22,49</t>
+          <t>18,31; 19,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,8; 19,55</t>
+          <t>18,77; 19,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,16; 20,4</t>
+          <t>19,26; 20,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,87; 19,85</t>
+          <t>18,88; 19,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,91; 20,85</t>
+          <t>19,04; 21,04</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19,75</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20,08</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19,16</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19,59</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>19,14</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>18,9</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>18,37</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>18,57</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>19,75</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>20,08</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>19,16</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,49</t>
+          <t>18,78</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,09</t>
+          <t>19,23</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,77; 19,57</t>
+          <t>19,19; 20,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,4; 19,46</t>
+          <t>19,37; 21,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,99; 18,86</t>
+          <t>18,6; 19,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,0; 19,16</t>
+          <t>19,11; 20,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,22; 20,61</t>
+          <t>18,77; 19,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,38; 20,97</t>
+          <t>18,38; 19,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,65; 19,94</t>
+          <t>17,95; 18,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,99; 20,0</t>
+          <t>18,27; 19,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,1; 19,93</t>
+          <t>19,13; 19,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,1; 20,09</t>
+          <t>19,09; 20,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,42; 19,21</t>
+          <t>18,44; 19,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,71; 19,52</t>
+          <t>18,84; 19,66</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20,5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19,7</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18,19</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>19,29</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>19,58</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>19,51</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>18,45</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19,47</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20,5</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,7</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,19</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19,17</t>
+          <t>18,83</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,32</t>
+          <t>19,07</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,87; 20,48</t>
+          <t>19,66; 22,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,77; 20,3</t>
+          <t>18,82; 20,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,87; 19,28</t>
+          <t>17,68; 18,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,43; 21,35</t>
+          <t>18,55; 20,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,58; 21,8</t>
+          <t>18,89; 20,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,95; 20,84</t>
+          <t>18,79; 20,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,66; 18,72</t>
+          <t>17,91; 19,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,52; 20,08</t>
+          <t>18,18; 20,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,51; 20,94</t>
+          <t>19,43; 20,85</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,09; 20,3</t>
+          <t>19,09; 20,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,93; 18,83</t>
+          <t>17,93; 18,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,72; 20,57</t>
+          <t>18,56; 19,71</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19,56</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19,91</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19,57</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18,54</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>18,66</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>19,4</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>19,33</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18,78</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,56</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,91</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,57</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,53</t>
+          <t>18,64</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,65</t>
+          <t>18,6</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,16; 19,25</t>
+          <t>18,92; 20,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,86; 20,05</t>
+          <t>19,17; 21,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,74; 20,19</t>
+          <t>18,91; 20,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,12; 19,81</t>
+          <t>18,09; 19,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,93; 20,51</t>
+          <t>18,18; 19,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,11; 21,75</t>
+          <t>18,87; 20,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,86; 20,51</t>
+          <t>18,72; 20,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,05; 19,1</t>
+          <t>18,08; 19,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,7; 19,7</t>
+          <t>18,67; 19,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,19; 20,54</t>
+          <t>19,15; 20,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,95; 20,04</t>
+          <t>18,96; 19,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,25; 19,22</t>
+          <t>18,19; 19,04</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>19,78</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19,94</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19,11</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19,41</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>19,01</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>19,29</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>18,82</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>18,96</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>19,78</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>19,94</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,11</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,3</t>
+          <t>18,8</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,14</t>
+          <t>19,12</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,72; 19,28</t>
+          <t>19,45; 20,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,97; 19,64</t>
+          <t>19,56; 20,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,53; 19,14</t>
+          <t>18,8; 19,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,56; 19,66</t>
+          <t>19,06; 19,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,46; 20,24</t>
+          <t>18,75; 19,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,55; 20,53</t>
+          <t>18,99; 19,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,75; 19,46</t>
+          <t>18,55; 19,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,94; 19,78</t>
+          <t>18,48; 19,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,18; 19,66</t>
+          <t>19,18; 19,68</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,35; 19,94</t>
+          <t>19,37; 19,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,73; 19,21</t>
+          <t>18,73; 19,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,87; 19,51</t>
+          <t>18,87; 19,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/imc_inf-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/imc_inf-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores, declarado por los/as progenitores/as (tasa de respuesta: 87,47%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, declarado por madres/padres (tasa de respuesta: 79,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>19,46</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>20,05</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19,46</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20,32</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>18,78</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,44</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,22</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19,04</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>19,14</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>19,76</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>19,34</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>19,7</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>19.4613967527058</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>20.05489561946084</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>19.46446756383776</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>20.3161460499225</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>18.78184564548475</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>19.44261751489444</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>19.2166955705742</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>19.03561010606018</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>19.14260522730576</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>19.76113971976681</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>19.34460419460082</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>19.70443459300244</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>18,86; 19,96</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>19,4; 21,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18,79; 20,27</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19,15; 22,31</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>18,26; 19,3</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18,67; 20,45</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>18,61; 19,9</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18,31; 19,74</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18,77; 19,53</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>19,26; 20,44</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>18,88; 19,86</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>19,04; 21,04</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>18.8592180406435</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>19.39728521856161</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>18.78941745853037</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>19.1488696146898</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>18.25904861262125</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>18.66730991697449</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>18.61002030918027</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>18.3079813402084</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>18.77253439734883</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>19.26385511873559</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>18.87642179370485</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>19.03636219002756</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>19.95504185351288</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>20.99654476850099</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>20.27490820734969</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>22.31408344867175</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>19.30081260430767</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>20.44502295786967</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>19.90076492961431</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>19.73802370693041</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>19.5268752590721</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>20.43507602213336</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>19.857019730479</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>21.04209682544982</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>19,75</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>20,08</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>19,16</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>19,59</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>19,14</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>18,9</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,37</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>18,78</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>19,46</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>19,51</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>18,79</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>19,23</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>19,19; 20,5</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>19,37; 21,1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>18,6; 19,88</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19,11; 20,19</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>18,77; 19,62</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,38; 19,44</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,95; 18,81</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18,27; 19,43</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>19,13; 19,93</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>19,09; 20,08</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18,44; 19,24</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>18,84; 19,66</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>19.75467636313939</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>20.0809558864252</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>19.16237743431587</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>19.59435059811013</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>19.14280400492002</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>18.90498530464784</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>18.37232579323718</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>18.77670816402239</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>19.45760726257566</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>19.51382893742421</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>18.78801092105331</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>19.22950710016366</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>20,5</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>19,7</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18,19</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19,29</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,58</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,51</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,45</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18,83</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>20,05</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>19,61</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>18,31</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>19,07</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>19.19084563174205</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>19.37259850321982</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>18.5967354903537</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>19.11279607280147</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>18.77377162379029</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>18.37843341261729</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>17.94900584915638</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>18.26544177164346</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>19.12742451672493</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>19.09399240188959</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>18.43605887112339</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>18.84026216685399</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>19,66; 22,03</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>18,82; 20,72</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>17,68; 18,85</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>18,55; 20,31</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>18,89; 20,44</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>18,79; 20,28</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>17,91; 19,15</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>18,18; 20,0</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>19,43; 20,85</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>19,09; 20,23</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>17,93; 18,77</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>18,56; 19,71</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>20.50339889344431</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>21.10492480594374</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>19.88118363237922</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>20.18902763673663</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>19.61950557779338</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>19.44177664974792</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>18.80687698049465</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>19.42719652361855</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>19.92620699508297</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>20.08346053247998</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>19.24085154976916</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>19.66030242948711</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>19,56</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>19,91</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19,57</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18,54</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18,66</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,33</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18,64</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>19,11</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>19,66</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>19,45</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>18,6</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>20.50016605248927</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>19.69800888796917</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>18.18806164514674</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>19.29193470894767</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>19.57997824900822</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>19.51312586915824</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>18.44623794430353</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>18.82978042426446</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>20.0540466874705</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>19.60829879216638</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>18.31177259550872</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>19.07318591147598</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>18,92; 20,57</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>19,17; 21,57</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18,91; 20,51</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>18,09; 19,09</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>18,18; 19,27</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>18,87; 20,01</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>18,72; 20,21</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>18,08; 19,42</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>18,67; 19,59</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>19,15; 20,53</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>18,96; 19,99</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>18,19; 19,04</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>19.66320193378943</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>18.82151653172427</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>17.67769447010164</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>18.55335154503524</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>18.88861579945813</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>18.79312079314646</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>17.90658265477336</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>18.18334179778232</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>19.43231705038505</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>19.09083671091015</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>17.92579947963026</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>18.56072263383963</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>22.02550854007814</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>20.71520902675574</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>18.84919388839169</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>20.30727633626039</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>20.44466119050719</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>20.2830690890276</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>19.15344114168397</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>19.99676324995565</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>20.85290281302776</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>20.22924925843327</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>18.77041534723905</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>19.70934469977148</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>19.56116489413847</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>19.90798685208229</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>19.5684622498891</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>18.54433598944632</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>18.66338492042554</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>19.39926816490237</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>19.33174822370906</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>18.64499317756678</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>19.10523013384671</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>19.65568355000713</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>19.45166639191235</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>18.59501972493329</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>18.91607907651624</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>19.17000104845437</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>18.91122214660395</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>18.09161185111113</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>18.17690285447914</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>18.87478775369863</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>18.72236721729177</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>18.08028527869434</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>18.67494623990493</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>19.14502496908344</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>18.9611001455708</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>18.1908801039081</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>20.57258938211776</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>21.56984744405224</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>20.50592747337465</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>19.09064859120312</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>19.2728502911465</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>20.01081480342258</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>20.21468423955761</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>19.42436601143718</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>19.58809033124861</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>20.52665986313614</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>19.99043796163523</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>19.04397861360488</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>19,78</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>19,94</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19,11</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19,41</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>19,01</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>19,29</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>18,82</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>18,8</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>19,41</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>19,62</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>18,97</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>19,12</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>19,45; 20,22</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>19,56; 20,52</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>18,8; 19,51</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19,06; 19,89</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>18,75; 19,3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,99; 19,62</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,55; 19,16</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18,48; 19,16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>19,18; 19,68</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>19,37; 19,93</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18,73; 19,2</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>18,87; 19,44</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>19.7837111511778</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>19.94200608123299</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>19.10766551521962</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>19.40675793458474</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>19.00870532088818</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>19.2863330261248</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>18.82493221474763</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>18.80349289378798</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>19.40517326971147</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>19.62311870058403</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>18.97125170427613</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>19.12146496951738</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>19.44555463527815</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>19.55537650236031</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>18.80035537625711</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>19.06347902053687</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>18.74685702743109</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>18.98891526856099</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>18.55349939543848</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>18.47961987585568</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>19.17947951219681</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>19.3721402912312</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>18.72806457421745</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>18.8652289471682</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>20.22230863420729</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>20.52483129221245</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>19.50517297894157</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>19.88734830565901</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>19.2959412618326</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>19.61634376037163</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>19.16249397821689</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>19.16370767472501</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>19.67735933811362</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>19.92649567862192</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>19.19865690315783</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>19.44482765185813</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/imc_inf-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/imc_inf-Habitat-trans_orig.xlsx
@@ -531,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores, declarado por madres/padres (tasa de respuesta: 79,86%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, declarado por madres/padres (tasa de respuesta: 87,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
